--- a/问题三/results/指定日期结果.xlsx
+++ b/问题三/results/指定日期结果.xlsx
@@ -538,13 +538,13 @@
         <v>18148.5431365</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>3073.341370833332</v>
+        <v>3073.341370833333</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>41663.25466204186</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>13490.57352893124</v>
+        <v>13490.57352893125</v>
       </c>
       <c r="J2" s="1" t="n">
         <v>57118.27455369173</v>
@@ -556,13 +556,13 @@
         <v>1894.723395804525</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>1894.723395804526</v>
+        <v>1894.723395804524</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>3.296918293926865e-12</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>1964.446362718625</v>
+        <v>1964.44636271862</v>
       </c>
     </row>
     <row r="3">
@@ -632,16 +632,16 @@
         <v>17022.45286533333</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>3215.938223666672</v>
+        <v>3215.93822366667</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>43341.14766613098</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>13942.8252625452</v>
+        <v>13942.82526254518</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>57283.97292867618</v>
+        <v>57283.97292867616</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>68149.93810955966</v>
@@ -653,10 +653,10 @@
         <v>0</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>2.501110429875553e-12</v>
+        <v>0</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>1.570822405483341e-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -697,13 +697,13 @@
         <v>807.8271197530703</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>807.8271197530872</v>
+        <v>807.8271197530861</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>3.183231456205249e-12</v>
+        <v>1.591615728102624e-12</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>789.8467119454662</v>
+        <v>789.8467119454631</v>
       </c>
     </row>
   </sheetData>

--- a/问题三/results/指定日期结果.xlsx
+++ b/问题三/results/指定日期结果.xlsx
@@ -529,40 +529,40 @@
         <v>55439.41991666666</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>67445.61404686215</v>
+        <v>69613.19349317592</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>22405.60881049382</v>
+        <v>21596.96929178292</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>18148.5431365</v>
+        <v>17729.63156329166</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>3073.341370833333</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>41663.25466204186</v>
+        <v>42678.31295021789</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>13490.57352893125</v>
+        <v>4.221192284603603e-13</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>57118.27455369173</v>
+        <v>43333.27212716051</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>69340.33744266667</v>
+        <v>70155.34207884259</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>1894.723395804525</v>
+        <v>542.1485856666695</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>1894.723395804524</v>
+        <v>542.1485856666743</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>1964.44636271862</v>
+        <v>654.9591769426219</v>
       </c>
     </row>
     <row r="3">
@@ -576,40 +576,40 @@
         <v>62073.3244</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>33899.99171666666</v>
+        <v>36472.10825992849</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>16000</v>
+        <v>18883.36936347737</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>12960</v>
+        <v>14814.03489862501</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1081.070016666666</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>19522.167056405</v>
+        <v>22225.35344453021</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>3908.685718749998</v>
+        <v>1.622311174287461e-13</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>23870.5296505125</v>
+        <v>22225.35344453021</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>34542.15811666666</v>
+        <v>36472.10825992849</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>642.1663999999946</v>
+        <v>0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>642.1663999999971</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>439.6768753574976</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -623,40 +623,40 @@
         <v>59065.66575</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>68149.93810955966</v>
+        <v>70029.95197418414</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>21015.37390781894</v>
+        <v>19569.29375598867</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>17022.45286533333</v>
+        <v>15793.47371879013</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>3215.93822366667</v>
+        <v>6.375000000000114</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>43341.14766613098</v>
+        <v>44993.04206758746</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>13942.82526254518</v>
+        <v>42.99618750000046</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>57283.97292867616</v>
+        <v>45086.12902399746</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>68149.93810955966</v>
+        <v>70073.63832418414</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>0</v>
+        <v>43.68635000000359</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>0</v>
+        <v>43.68634999999995</v>
       </c>
       <c r="N4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>0</v>
+        <v>50.09076890999994</v>
       </c>
     </row>
     <row r="5">
@@ -670,40 +670,40 @@
         <v>35338.6591</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>93776.07118950617</v>
+        <v>93129.12472582862</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>25645.24005925926</v>
+        <v>23740.06694813695</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>20772.644448</v>
+        <v>19245.38228690605</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>2465.557035333339</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>59565.76703284562</v>
+        <v>61323.82163026267</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>11224.82064171369</v>
+        <v>4.888534022029489e-13</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>71580.43438650477</v>
+        <v>62491.37074447008</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>94583.89830925924</v>
+        <v>93728.07762789755</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>807.8271197530703</v>
+        <v>598.952902068937</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>807.8271197530861</v>
+        <v>598.9529020689498</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>1.591615728102624e-12</v>
+        <v>0</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>789.8467119454631</v>
+        <v>1167.549114207409</v>
       </c>
     </row>
   </sheetData>

--- a/问题三/results/指定日期结果.xlsx
+++ b/问题三/results/指定日期结果.xlsx
@@ -529,40 +529,40 @@
         <v>55439.41991666666</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>69613.19349317592</v>
+        <v>67439.61595818795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>21596.96929178292</v>
+        <v>19352.51126385451</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>17729.63156329166</v>
+        <v>17600.88079212654</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>407.8953815000039</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>42678.31295021789</v>
+        <v>41708.3680995156</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>4.221192284603603e-13</v>
+        <v>2006.422638056936</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>43333.27212716051</v>
+        <v>43714.79073757254</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>70155.34207884259</v>
+        <v>67439.61595818795</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>542.1485856666695</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>542.1485856666743</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>654.9591769426219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -576,28 +576,28 @@
         <v>62073.3244</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>36472.10825992849</v>
+        <v>35990.10046714616</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>18883.36936347737</v>
+        <v>14157.49606378601</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>14814.03489862501</v>
+        <v>11237.15589627976</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>5.684341886080801e-14</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>22225.35344453021</v>
+        <v>21884.94369969972</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>1.622311174287461e-13</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>22225.35344453021</v>
+        <v>21884.94369969972</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>36472.10825992849</v>
+        <v>35990.10046714616</v>
       </c>
       <c r="L3" s="1" t="n">
         <v>0</v>
@@ -623,40 +623,40 @@
         <v>59065.66575</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>70029.95197418414</v>
+        <v>68213.01807778841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>19569.29375598867</v>
+        <v>19245.54905312125</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>15793.47371879013</v>
+        <v>16071.6907706131</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>6.375000000000114</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>44993.04206758746</v>
+        <v>44123.78746673523</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>42.99618750000046</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>45086.12902399746</v>
+        <v>44191.86991976143</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>70073.63832418414</v>
+        <v>68172.9505717571</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>43.68635000000359</v>
+        <v>-40.06750603130786</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>43.68634999999995</v>
+        <v>0</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>0</v>
+        <v>40.06750603130899</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>50.09076890999994</v>
+        <v>25.08626552620256</v>
       </c>
     </row>
     <row r="5">
@@ -670,40 +670,40 @@
         <v>35338.6591</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>93129.12472582862</v>
+        <v>93419.00366283522</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>23740.06694813695</v>
+        <v>22987.91859762328</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>19245.38228690605</v>
+        <v>17997.04202534358</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>1.13686837721616e-13</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>61323.82163026267</v>
+        <v>61468.77392504711</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>4.888534022029489e-13</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>62491.37074447008</v>
+        <v>63192.57499651201</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>93728.07762789755</v>
+        <v>95502.58920908008</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>598.952902068937</v>
+        <v>2083.585546244853</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>598.9529020689498</v>
+        <v>2083.58554624486</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>1167.549114207409</v>
+        <v>1723.801071464906</v>
       </c>
     </row>
   </sheetData>
